--- a/Exam/gymtrackerpro/lib/schema/__tests__/bbt/user-schema/createMemberWithTempPasswordSchema-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/schema/__tests__/bbt/user-schema/createMemberWithTempPasswordSchema-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="165">
-  <si>
-    <t>Statement: createMemberWithTempPasswordSchema – validate input for creating a member whose password is auto-generated.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="164">
+  <si>
+    <t>Statement: createMemberWithTempPasswordSchema – Validates the input for creating a member whose password is auto-generated. Returns { success: true, data } when all required fields satisfy their constraints. Returns { success: false, error } with a path pointing to the offending field on any violation. Required fields: email (valid email format), fullName (8–64 characters after trimming, not whitespace-only), phone (E.164 format: +[1-9]\d{1,14}), dateOfBirth (YYYY-MM-DD, strictly before today), membershipStart (YYYY-MM-DD; future dates accepted). The password field is not required and is stripped from the parsed output if supplied. Surrounding whitespace is trimmed from fullName, email, and phone before validation.</t>
   </si>
   <si>
     <t/>
@@ -31,25 +31,25 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: { email: string, fullName: string, phone: string, dateOfBirth: string, membershipStart: string }</t>
+    <t>Input: { email: string, fullName: string, phone: string, dateOfBirth: string, membershipStart: string, password?: string (ignored) }</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>8 ≤ len(fullName) ≤ 64 | email valid RFC | dateOfBirth past | phone E.164 | membershipStart YYYY-MM-DD</t>
+    <t>Input is passed directly to createMemberWithTempPasswordSchema.safeParse(). fullName rules: 8–64 characters after trim, not whitespace-only. dateOfBirth: YYYY-MM-DD, strictly before today (yesterday is valid, today is not). membershipStart: YYYY-MM-DD, any date including future. password: silently stripped if present.</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: { success: true, data } OR { success: false, error }</t>
+    <t>Output: { success: boolean, data?: CreateMemberWithTempPasswordInput, error?: ZodError }</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t>password field is stripped if supplied.</t>
+    <t>On success: parsed data matches the (trimmed) input and contains no password field. On failure: error.issues[0].path contains the name of the offending field.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -64,73 +64,85 @@
     <t>Invalid EC</t>
   </si>
   <si>
-    <t>All fields valid</t>
-  </si>
-  <si>
-    <t>All fields correct</t>
-  </si>
-  <si>
-    <t>Email presence</t>
-  </si>
-  <si>
-    <t>Present</t>
-  </si>
-  <si>
-    <t>Missing</t>
-  </si>
-  <si>
-    <t>FullName presence</t>
-  </si>
-  <si>
-    <t>Phone presence</t>
-  </si>
-  <si>
-    <t>DateOfBirth presence</t>
-  </si>
-  <si>
-    <t>MembershipStart presence</t>
-  </si>
-  <si>
-    <t>Email format</t>
-  </si>
-  <si>
-    <t>Valid RFC</t>
-  </si>
-  <si>
-    <t>Invalid format</t>
-  </si>
-  <si>
-    <t>Phone format</t>
-  </si>
-  <si>
-    <t>Valid E.164</t>
-  </si>
-  <si>
-    <t>MembershipStart format</t>
-  </si>
-  <si>
-    <t>YYYY-MM-DD</t>
-  </si>
-  <si>
-    <t>Password field</t>
-  </si>
-  <si>
-    <t>Ignored and stripped</t>
-  </si>
-  <si>
-    <t>FullName whitespace</t>
-  </si>
-  <si>
-    <t>Surrounding whitespace (trimmed)</t>
-  </si>
-  <si>
-    <t>Whitespace-only</t>
-  </si>
-  <si>
-    <t>Email whitespace</t>
-  </si>
-  <si>
-    <t>Phone whitespace</t>
+    <t>Input validity</t>
+  </si>
+  <si>
+    <t>All required fields valid → success: true, parsed data equals input</t>
+  </si>
+  <si>
+    <t>email presence</t>
+  </si>
+  <si>
+    <t>email omitted → success: false, error path contains "email"</t>
+  </si>
+  <si>
+    <t>fullName presence</t>
+  </si>
+  <si>
+    <t>fullName omitted → success: false, error path contains "fullName"</t>
+  </si>
+  <si>
+    <t>phone presence</t>
+  </si>
+  <si>
+    <t>phone omitted → success: false, error path contains "phone"</t>
+  </si>
+  <si>
+    <t>dateOfBirth presence</t>
+  </si>
+  <si>
+    <t>dateOfBirth omitted → success: false, error path contains "dateOfBirth"</t>
+  </si>
+  <si>
+    <t>membershipStart presence</t>
+  </si>
+  <si>
+    <t>membershipStart omitted → success: false, error path contains "membershipStart"</t>
+  </si>
+  <si>
+    <t>email format</t>
+  </si>
+  <si>
+    <t>email: "no" (no @ sign) → success: false, error path contains "email"</t>
+  </si>
+  <si>
+    <t>phone format</t>
+  </si>
+  <si>
+    <t>phone: "0712345678" (no country code prefix) → success: false, error path contains "phone"</t>
+  </si>
+  <si>
+    <t>membershipStart format</t>
+  </si>
+  <si>
+    <t>membershipStart: "01/01/2024" (MM/DD/YYYY, wrong format) → success: false, error path contains "membershipStart"</t>
+  </si>
+  <si>
+    <t>password field</t>
+  </si>
+  <si>
+    <t>password field supplied alongside required fields → success: true, parsed output contains no password field</t>
+  </si>
+  <si>
+    <t>fullName content</t>
+  </si>
+  <si>
+    <t>fullName: "  Jane Doe Test  " (surrounding whitespace) → success: true, parsed fullName is "Jane Doe Test"</t>
+  </si>
+  <si>
+    <t>fullName: "         " (whitespace-only) → success: false, error path contains "fullName"</t>
+  </si>
+  <si>
+    <t>email whitespace</t>
+  </si>
+  <si>
+    <t>email: "  jane.doe@example.com  " (surrounding whitespace) → success: true, parsed email is "jane.doe@example.com"</t>
+  </si>
+  <si>
+    <t>phone whitespace</t>
+  </si>
+  <si>
+    <t>phone: "  +40712345678  " (surrounding whitespace) → success: true, parsed phone is "+40712345678"</t>
   </si>
   <si>
     <t>No TC</t>
@@ -151,10 +163,10 @@
     <t>EC-1</t>
   </si>
   <si>
-    <t>Valid member data</t>
-  </si>
-  <si>
-    <t>success: true</t>
+    <t>all required fields provided with valid values (no password field)</t>
+  </si>
+  <si>
+    <t>success: true, parsed data equals input</t>
   </si>
   <si>
     <t>Passed</t>
@@ -163,82 +175,103 @@
     <t>EC-2</t>
   </si>
   <si>
-    <t>Missing email</t>
-  </si>
-  <si>
-    <t>success: false</t>
+    <t>valid member data with email field omitted</t>
+  </si>
+  <si>
+    <t>success: false, error path contains "email"</t>
   </si>
   <si>
     <t>EC-3</t>
   </si>
   <si>
-    <t>Missing fullName</t>
+    <t>valid member data with fullName field omitted</t>
+  </si>
+  <si>
+    <t>success: false, error path contains "fullName"</t>
   </si>
   <si>
     <t>EC-4</t>
   </si>
   <si>
-    <t>Missing phone</t>
+    <t>valid member data with phone field omitted</t>
+  </si>
+  <si>
+    <t>success: false, error path contains "phone"</t>
   </si>
   <si>
     <t>EC-5</t>
   </si>
   <si>
-    <t>Missing dateOfBirth</t>
+    <t>valid member data with dateOfBirth field omitted</t>
+  </si>
+  <si>
+    <t>success: false, error path contains "dateOfBirth"</t>
   </si>
   <si>
     <t>EC-6</t>
   </si>
   <si>
-    <t>Missing membershipStart</t>
+    <t>valid member data with membershipStart field omitted</t>
+  </si>
+  <si>
+    <t>success: false, error path contains "membershipStart"</t>
   </si>
   <si>
     <t>EC-7</t>
   </si>
   <si>
-    <t>Email="no" (Invalid)</t>
+    <t>valid member data with email: "no" (no @ sign)</t>
   </si>
   <si>
     <t>EC-8</t>
   </si>
   <si>
-    <t>Phone="0712345678" (Invalid)</t>
+    <t>valid member data with phone: "0712345678" (no country code prefix)</t>
   </si>
   <si>
     <t>EC-9</t>
   </si>
   <si>
-    <t>MembershipStart="01/01/2024" (Invalid format)</t>
+    <t>valid member data with membershipStart: "01/01/2024" (MM/DD/YYYY, wrong format)</t>
   </si>
   <si>
     <t>EC-10</t>
   </si>
   <si>
-    <t>Including password field</t>
-  </si>
-  <si>
-    <t>success: true, password stripped</t>
+    <t>all required fields valid, an extra password field is included alongside the required fields</t>
+  </si>
+  <si>
+    <t>success: true, parsed output contains no password field</t>
   </si>
   <si>
     <t>EC-11</t>
   </si>
   <si>
-    <t>fullName="         " (whitespace only)</t>
-  </si>
-  <si>
-    <t>fullName="  Jane Doe Test  " (padded)</t>
+    <t>valid member data with fullName: "         " (whitespace-only)</t>
+  </si>
+  <si>
+    <t>valid member data with fullName: "  Jane Doe Test  " (surrounding whitespace)</t>
+  </si>
+  <si>
+    <t>success: true, parsed fullName is "Jane Doe Test"</t>
   </si>
   <si>
     <t>EC-12</t>
   </si>
   <si>
-    <t>email="  jane.doe@example.com  " (padded)</t>
+    <t>valid member data with email: "  jane.doe@example.com  " (surrounding whitespace)</t>
+  </si>
+  <si>
+    <t>success: true, parsed email is "jane.doe@example.com"</t>
   </si>
   <si>
     <t>EC-13</t>
   </si>
   <si>
-    <t>phone="  +40712345678  " (padded)</t>
+    <t>valid member data with phone: "  +40712345678  " (surrounding whitespace)</t>
+  </si>
+  <si>
+    <t>success: true, parsed phone is "+40712345678"</t>
   </si>
   <si>
     <t>Number BVA</t>
@@ -247,130 +280,148 @@
     <t>BVA Test Case</t>
   </si>
   <si>
-    <t>FullName length</t>
-  </si>
-  <si>
-    <t>7 chars (Below Min)</t>
-  </si>
-  <si>
-    <t>8 chars (At Min)</t>
-  </si>
-  <si>
-    <t>9 chars (Above Min)</t>
-  </si>
-  <si>
-    <t>63 chars (Below Max)</t>
-  </si>
-  <si>
-    <t>64 chars (At Max)</t>
-  </si>
-  <si>
-    <t>65 chars (Above Max)</t>
-  </si>
-  <si>
-    <t>DateOfBirth boundary</t>
-  </si>
-  <si>
-    <t>Yesterday (Valid)</t>
-  </si>
-  <si>
-    <t>Today (Invalid)</t>
-  </si>
-  <si>
-    <t>Tomorrow (Invalid)</t>
-  </si>
-  <si>
-    <t>8 whitespace chars (Whitespace At Min)</t>
-  </si>
-  <si>
-    <t>8 chars padded with whitespace (At Min after trim)</t>
-  </si>
-  <si>
-    <t>64 chars padded with whitespace (At Max after trim)</t>
-  </si>
-  <si>
-    <t>65 chars padded with whitespace (Above Max after trim)</t>
+    <t>fullName length</t>
+  </si>
+  <si>
+    <t>fullName: "A".repeat(7) (min - 1): below minimum → success: false</t>
+  </si>
+  <si>
+    <t>fullName: "A".repeat(8) (min): at minimum → success: true, parsed fullName is "A".repeat(8)</t>
+  </si>
+  <si>
+    <t>fullName: "A".repeat(9) (min + 1): above minimum → success: true, parsed fullName is "A".repeat(9)</t>
+  </si>
+  <si>
+    <t>fullName: "A".repeat(63) (max - 1): below maximum → success: true, parsed fullName is "A".repeat(63)</t>
+  </si>
+  <si>
+    <t>fullName: "A".repeat(64) (max): at maximum → success: true, parsed fullName is "A".repeat(64)</t>
+  </si>
+  <si>
+    <t>fullName: "A".repeat(65) (max + 1): above maximum → success: false</t>
+  </si>
+  <si>
+    <t>dateOfBirth boundary</t>
+  </si>
+  <si>
+    <t>dateOfBirth: yesterday (one day before today, YYYY-MM-DD): strictly before today → success: true</t>
+  </si>
+  <si>
+    <t>dateOfBirth: today (YYYY-MM-DD): not before today → success: false</t>
+  </si>
+  <si>
+    <t>dateOfBirth: tomorrow (one day after today, YYYY-MM-DD): future → success: false</t>
+  </si>
+  <si>
+    <t>fullName whitespace + trim</t>
+  </si>
+  <si>
+    <t>fullName: " ".repeat(8) (8 whitespace chars, empty after trim) → success: false</t>
+  </si>
+  <si>
+    <t>fullName: " " + "A".repeat(8) + " " (8 real chars after trim, at minimum) → success: true, parsed fullName is "A".repeat(8)</t>
+  </si>
+  <si>
+    <t>fullName: " " + "A".repeat(64) + " " (64 real chars after trim, at maximum) → success: true, parsed fullName is "A".repeat(64)</t>
+  </si>
+  <si>
+    <t>fullName: " " + "A".repeat(65) + " " (65 real chars after trim, above maximum) → success: false</t>
   </si>
   <si>
     <t>BVA</t>
   </si>
   <si>
-    <t>BVA-1 FullName 7ch</t>
-  </si>
-  <si>
-    <t>fullName len 7</t>
-  </si>
-  <si>
-    <t>BVA-1 FullName 8ch</t>
-  </si>
-  <si>
-    <t>fullName len 8</t>
-  </si>
-  <si>
-    <t>BVA-1 FullName 9ch</t>
-  </si>
-  <si>
-    <t>fullName len 9</t>
-  </si>
-  <si>
-    <t>BVA-1 FullName 63ch</t>
-  </si>
-  <si>
-    <t>fullName len 63</t>
-  </si>
-  <si>
-    <t>BVA-1 FullName 64ch</t>
-  </si>
-  <si>
-    <t>fullName len 64</t>
-  </si>
-  <si>
-    <t>BVA-1 FullName 65ch</t>
-  </si>
-  <si>
-    <t>fullName len 65</t>
-  </si>
-  <si>
-    <t>BVA-2 DOB Yesterday</t>
-  </si>
-  <si>
-    <t>dob Yesterday</t>
-  </si>
-  <si>
-    <t>BVA-2 DOB Today</t>
-  </si>
-  <si>
-    <t>dob Today</t>
-  </si>
-  <si>
-    <t>BVA-2 DOB Tomorrow</t>
-  </si>
-  <si>
-    <t>dob Tomorrow</t>
-  </si>
-  <si>
-    <t>BVA-3 FullName whitespace 8ch</t>
-  </si>
-  <si>
-    <t>fullName=" ".repeat(8)</t>
-  </si>
-  <si>
-    <t>BVA-3 FullName padded 8ch after trim</t>
-  </si>
-  <si>
-    <t>fullName=" "+"A".repeat(8)+" "</t>
-  </si>
-  <si>
-    <t>BVA-3 FullName padded 64ch after trim</t>
-  </si>
-  <si>
-    <t>fullName=" "+"A".repeat(64)+" "</t>
-  </si>
-  <si>
-    <t>BVA-3 FullName padded 65ch after trim</t>
-  </si>
-  <si>
-    <t>fullName=" "+"A".repeat(65)+" "</t>
+    <t>BVA-1  (fullName=7)</t>
+  </si>
+  <si>
+    <t>valid member data (no password) with fullName: "A".repeat(7) (7 characters)</t>
+  </si>
+  <si>
+    <t>BVA-2  (fullName=8)</t>
+  </si>
+  <si>
+    <t>valid member data (no password) with fullName: "A".repeat(8) (8 characters)</t>
+  </si>
+  <si>
+    <t>success: true, parsed fullName is "A".repeat(8)</t>
+  </si>
+  <si>
+    <t>BVA-3  (fullName=9)</t>
+  </si>
+  <si>
+    <t>valid member data (no password) with fullName: "A".repeat(9) (9 characters)</t>
+  </si>
+  <si>
+    <t>success: true, parsed fullName is "A".repeat(9)</t>
+  </si>
+  <si>
+    <t>BVA-4  (fullName=63)</t>
+  </si>
+  <si>
+    <t>valid member data (no password) with fullName: "A".repeat(63) (63 characters)</t>
+  </si>
+  <si>
+    <t>success: true, parsed fullName is "A".repeat(63)</t>
+  </si>
+  <si>
+    <t>BVA-5  (fullName=64)</t>
+  </si>
+  <si>
+    <t>valid member data (no password) with fullName: "A".repeat(64) (64 characters)</t>
+  </si>
+  <si>
+    <t>success: true, parsed fullName is "A".repeat(64)</t>
+  </si>
+  <si>
+    <t>BVA-6  (fullName=65)</t>
+  </si>
+  <si>
+    <t>valid member data (no password) with fullName: "A".repeat(65) (65 characters)</t>
+  </si>
+  <si>
+    <t>BVA-7  (dob=yest)</t>
+  </si>
+  <si>
+    <t>valid member data (no password) with dateOfBirth set to yesterday (one day before today, YYYY-MM-DD)</t>
+  </si>
+  <si>
+    <t>success: true, parsed dateOfBirth is yesterday's date string</t>
+  </si>
+  <si>
+    <t>BVA-8  (dob=today)</t>
+  </si>
+  <si>
+    <t>valid member data (no password) with dateOfBirth set to today (YYYY-MM-DD)</t>
+  </si>
+  <si>
+    <t>BVA-9  (dob=tmrw)</t>
+  </si>
+  <si>
+    <t>valid member data (no password) with dateOfBirth set to tomorrow (one day after today, YYYY-MM-DD)</t>
+  </si>
+  <si>
+    <t>BVA-10 (ws=8)</t>
+  </si>
+  <si>
+    <t>valid member data (no password) with fullName: " ".repeat(8) (8 whitespace characters, empty after trim)</t>
+  </si>
+  <si>
+    <t>BVA-11 (pad→8)</t>
+  </si>
+  <si>
+    <t>valid member data (no password) with fullName: " " + "A".repeat(8) + " " (8 real characters after trim)</t>
+  </si>
+  <si>
+    <t>BVA-12 (pad→64)</t>
+  </si>
+  <si>
+    <t>valid member data (no password) with fullName: " " + "A".repeat(64) + " " (64 real characters after trim)</t>
+  </si>
+  <si>
+    <t>BVA-13 (pad→65)</t>
+  </si>
+  <si>
+    <t>valid member data (no password) with fullName: " " + "A".repeat(65) + " " (65 real characters after trim)</t>
   </si>
   <si>
     <t>TC from EC</t>
@@ -379,97 +430,43 @@
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>Valid member data (No password needed)</t>
-  </si>
-  <si>
-    <t>Missing email field</t>
-  </si>
-  <si>
-    <t>Missing fullName field</t>
-  </si>
-  <si>
-    <t>Missing phone field</t>
-  </si>
-  <si>
-    <t>Missing dateOfBirth field</t>
-  </si>
-  <si>
-    <t>Missing membershipStart field</t>
-  </si>
-  <si>
-    <t>Email="no" (Invalid format)</t>
-  </si>
-  <si>
-    <t>Phone="0712345678" (Wrong format)</t>
-  </si>
-  <si>
-    <t>MembershipStart="01/01/2024" (Wrong separators)</t>
-  </si>
-  <si>
-    <t>Input contains extra password field</t>
-  </si>
-  <si>
-    <t>success: true (Stripped)</t>
-  </si>
-  <si>
-    <t>FullName whitespace-only</t>
-  </si>
-  <si>
-    <t>FullName with surrounding whitespace</t>
-  </si>
-  <si>
-    <t>Email with surrounding whitespace</t>
-  </si>
-  <si>
-    <t>Phone with surrounding whitespace</t>
-  </si>
-  <si>
     <t>BVA-1</t>
   </si>
   <si>
-    <t>fullName len 7 (Below Min)</t>
-  </si>
-  <si>
-    <t>fullName len 8 (At Min)</t>
-  </si>
-  <si>
-    <t>fullName len 9 (Above Min)</t>
-  </si>
-  <si>
-    <t>fullName len 63 (Below Max)</t>
-  </si>
-  <si>
-    <t>fullName len 64 (At Max)</t>
-  </si>
-  <si>
-    <t>fullName len 65 (Above Max)</t>
-  </si>
-  <si>
     <t>BVA-2</t>
   </si>
   <si>
-    <t>dob Yesterday (Valid)</t>
-  </si>
-  <si>
-    <t>dob Today (At boundary - invalid)</t>
-  </si>
-  <si>
-    <t>dob Tomorrow (Future - invalid)</t>
-  </si>
-  <si>
     <t>BVA-3</t>
   </si>
   <si>
-    <t>fullName whitespace 8ch</t>
-  </si>
-  <si>
-    <t>fullName padded → 8ch after trim (At Min)</t>
-  </si>
-  <si>
-    <t>fullName padded → 64ch after trim (At Max)</t>
-  </si>
-  <si>
-    <t>fullName padded → 65ch after trim (Above Max)</t>
+    <t>BVA-4</t>
+  </si>
+  <si>
+    <t>BVA-5</t>
+  </si>
+  <si>
+    <t>BVA-6</t>
+  </si>
+  <si>
+    <t>BVA-7</t>
+  </si>
+  <si>
+    <t>BVA-8</t>
+  </si>
+  <si>
+    <t>BVA-9</t>
+  </si>
+  <si>
+    <t>BVA-10</t>
+  </si>
+  <si>
+    <t>BVA-11</t>
+  </si>
+  <si>
+    <t>BVA-12</t>
+  </si>
+  <si>
+    <t>BVA-13</t>
   </si>
   <si>
     <t>Testing</t>
@@ -502,7 +499,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>MEM-01/MEM-02</t>
+    <t>SCHEMA-02</t>
   </si>
   <si>
     <t>n/a</t>
@@ -1071,10 +1068,10 @@
         <v>17</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1082,13 +1079,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1099,10 +1096,10 @@
         <v>21</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1110,13 +1107,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1124,13 +1121,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1138,13 +1135,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1152,13 +1149,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1166,13 +1163,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1180,10 +1177,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>1</v>
@@ -1194,13 +1191,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1208,10 +1205,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>1</v>
@@ -1222,10 +1219,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>1</v>
@@ -1251,19 +1248,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1271,16 +1268,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1288,16 +1285,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1305,16 +1302,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1322,16 +1319,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1339,16 +1336,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1356,16 +1353,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1373,16 +1370,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1390,16 +1387,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1407,16 +1404,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1424,16 +1421,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1441,16 +1438,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1458,16 +1455,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1475,16 +1472,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1492,16 +1489,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1522,13 +1519,13 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1536,142 +1533,142 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
+      <c r="A3" s="1">
+        <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>87</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>1</v>
+      <c r="A4" s="1">
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1</v>
+        <v>87</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>1</v>
+      <c r="A5" s="1">
+        <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1</v>
+        <v>87</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>1</v>
+      <c r="A6" s="1">
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1</v>
+        <v>87</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>1</v>
+      <c r="A7" s="1">
+        <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1</v>
+        <v>87</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>1</v>
+      <c r="A9" s="1">
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1</v>
+        <v>94</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>1</v>
+      <c r="A10" s="1">
+        <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>1</v>
+        <v>94</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>1</v>
+      <c r="A12" s="1">
+        <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>1</v>
+      <c r="A13" s="1">
+        <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>1</v>
+      <c r="A14" s="1">
+        <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -1694,19 +1691,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1714,16 +1711,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1731,16 +1728,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>45</v>
+        <v>108</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1748,16 +1745,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>45</v>
+        <v>111</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1765,16 +1762,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>45</v>
+        <v>114</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1782,16 +1779,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>45</v>
+        <v>117</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1799,16 +1796,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1816,16 +1813,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>45</v>
+        <v>122</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1833,16 +1830,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1850,16 +1847,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1867,16 +1864,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1884,16 +1881,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>45</v>
+        <v>108</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1901,16 +1898,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>45</v>
+        <v>117</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1918,16 +1915,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1951,22 +1948,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1974,19 +1971,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1994,19 +1991,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>121</v>
+        <v>52</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2014,19 +2011,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>122</v>
+        <v>55</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2034,19 +2031,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>123</v>
+        <v>58</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2054,19 +2051,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>124</v>
+        <v>61</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2074,19 +2071,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>125</v>
+        <v>64</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2094,19 +2091,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>126</v>
+        <v>67</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2114,19 +2111,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>127</v>
+        <v>69</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2134,19 +2131,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2154,19 +2151,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>129</v>
+        <v>73</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>130</v>
+        <v>74</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2174,19 +2171,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>131</v>
+        <v>76</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2194,19 +2191,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2214,19 +2211,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2234,19 +2231,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2257,16 +2254,16 @@
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2277,16 +2274,16 @@
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>45</v>
+        <v>108</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2297,16 +2294,16 @@
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>45</v>
+        <v>111</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2317,16 +2314,16 @@
         <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>45</v>
+        <v>114</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2337,16 +2334,16 @@
         <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>45</v>
+        <v>117</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2357,16 +2354,16 @@
         <v>1</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2377,16 +2374,16 @@
         <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>143</v>
+        <v>121</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>45</v>
+        <v>122</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2397,16 +2394,16 @@
         <v>1</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2417,16 +2414,16 @@
         <v>1</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2440,13 +2437,13 @@
         <v>146</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2457,16 +2454,16 @@
         <v>1</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>45</v>
+        <v>108</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2477,16 +2474,16 @@
         <v>1</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>45</v>
+        <v>117</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2497,16 +2494,16 @@
         <v>1</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -2534,16 +2531,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>153</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -2551,39 +2548,39 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>160</v>
-      </c>
       <c r="H2" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>156</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B3" s="1">
         <v>27</v>
@@ -2598,19 +2595,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>163</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>

--- a/Exam/gymtrackerpro/lib/schema/__tests__/bbt/user-schema/createMemberWithTempPasswordSchema-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/schema/__tests__/bbt/user-schema/createMemberWithTempPasswordSchema-bbt-form.xlsx
@@ -499,7 +499,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>SCHEMA-02</t>
+    <t>SCHEMA-03</t>
   </si>
   <si>
     <t>n/a</t>
